--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/5009-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/5009-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0934B282-CD01-4358-B8FE-626537712509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E89F7B16-CAF5-4C6B-9A28-F03DB2700789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{BA11D7C1-8112-42DD-9A9C-74AAFEF33BEA}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{51998152-485C-4AC1-AFA3-C76887FCBEDA}"/>
   </bookViews>
   <sheets>
     <sheet name="5009-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1526,25 +1526,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C810A03B-6E88-4607-9D41-4F440C3A8F81}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E26F49B7-E156-4A04-ADCE-B2DC0A091264}">
   <dimension ref="A1:R70"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1572,7 +1572,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1602,7 +1602,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1698,7 +1698,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1752,7 +1752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1808,7 +1808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="39">
         <v>2025</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>26</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>26</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="37">
         <v>2024</v>
       </c>
@@ -2196,7 +2196,7 @@
         <v>4.7699999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>4.7699999999999996</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2476,7 +2476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="39">
         <v>2023</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>4.08</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>26</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
@@ -2642,7 +2642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>26</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>26</v>
       </c>
@@ -2754,7 +2754,7 @@
         <v>4.08</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="37">
         <v>2022</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>5.42</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -3032,7 +3032,7 @@
         <v>5.42</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="39">
         <v>2021</v>
       </c>
@@ -3086,7 +3086,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
         <v>26</v>
       </c>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>26</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>26</v>
       </c>
@@ -3254,7 +3254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>26</v>
       </c>
@@ -3310,7 +3310,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>26</v>
       </c>
@@ -3366,7 +3366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2020</v>
       </c>
@@ -3420,7 +3420,7 @@
         <v>3.13</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>26</v>
       </c>
@@ -3476,7 +3476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>26</v>
       </c>
@@ -3532,7 +3532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>26</v>
       </c>
@@ -3588,7 +3588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>26</v>
       </c>
@@ -3644,7 +3644,7 @@
         <v>3.13</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>2019</v>
       </c>
@@ -3698,7 +3698,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="17" t="s">
         <v>26</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="17" t="s">
         <v>26</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
         <v>26</v>
       </c>
@@ -3866,7 +3866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="17" t="s">
         <v>26</v>
       </c>
@@ -3922,7 +3922,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="37">
         <v>2018</v>
       </c>
@@ -3976,7 +3976,7 @@
         <v>1.77</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="39">
         <v>2017</v>
       </c>
@@ -4030,7 +4030,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="37">
         <v>2016</v>
       </c>
@@ -4084,7 +4084,7 @@
         <v>5.78</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="39">
         <v>2015</v>
       </c>
@@ -4138,7 +4138,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="37">
         <v>2014</v>
       </c>
@@ -4192,7 +4192,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="39">
         <v>2013</v>
       </c>
@@ -4246,7 +4246,7 @@
         <v>4.6900000000000004</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="37">
         <v>2012</v>
       </c>
@@ -4300,7 +4300,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="39">
         <v>2011</v>
       </c>
@@ -4354,7 +4354,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="37">
         <v>2010</v>
       </c>
@@ -4408,7 +4408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="39">
         <v>2009</v>
       </c>
@@ -4462,7 +4462,7 @@
         <v>4.93</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="37">
         <v>2008</v>
       </c>
@@ -4516,7 +4516,7 @@
         <v>7.09</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="39">
         <v>2007</v>
       </c>
@@ -4570,7 +4570,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="37">
         <v>2006</v>
       </c>
@@ -4624,7 +4624,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="39">
         <v>2005</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>3.48</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="37">
         <v>2004</v>
       </c>
@@ -4732,7 +4732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="39">
         <v>2003</v>
       </c>
@@ -4786,7 +4786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="37">
         <v>2002</v>
       </c>
@@ -4840,7 +4840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="39">
         <v>2001</v>
       </c>
@@ -4894,7 +4894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="37">
         <v>2000</v>
       </c>
@@ -4948,7 +4948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="39">
         <v>1999</v>
       </c>
@@ -5002,7 +5002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="37">
         <v>1998</v>
       </c>
@@ -5056,7 +5056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="39">
         <v>1997</v>
       </c>
@@ -5110,7 +5110,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="37">
         <v>1996</v>
       </c>
@@ -5164,7 +5164,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="68" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="39">
         <v>1995</v>
       </c>
@@ -5218,7 +5218,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="69" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="37">
         <v>1994</v>
       </c>
@@ -5272,7 +5272,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="39" t="s">
         <v>61</v>
       </c>
